--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -140,13 +140,13 @@
     <t>ClinicalDocument.code</t>
   </si>
   <si>
-    <t>EnteteDocument.titre</t>
+    <t>EnteteDocument.titreDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.title</t>
   </si>
   <si>
-    <t>EnteteDocument.dateDeCreation</t>
+    <t>EnteteDocument.dateDeCreationDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.effectiveTime</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -146,7 +146,7 @@
     <t>ClinicalDocument.title</t>
   </si>
   <si>
-    <t>EnteteDocument.dateDeCreationDocument</t>
+    <t>EnteteDocument.dateDeCreation</t>
   </si>
   <si>
     <t>ClinicalDocument.effectiveTime</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -146,13 +146,13 @@
     <t>ClinicalDocument.title</t>
   </si>
   <si>
-    <t>EnteteDocument.dateDeCreation</t>
+    <t>EnteteDocument.dateDeCreationDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.effectiveTime</t>
   </si>
   <si>
-    <t>EnteteDocument.niveauConfidentialite</t>
+    <t>EnteteDocument.niveauConfidentialiteDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.confidentialityCode</t>
@@ -164,7 +164,7 @@
     <t>ClinicalDocument.languageCode</t>
   </si>
   <si>
-    <t>EnteteDocument.identifiantDuLotDeVersions</t>
+    <t>EnteteDocument.identifiantLotDeVersionsDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.setId</t>
@@ -179,124 +179,127 @@
     <t>EnteteDocument.StatutDocument</t>
   </si>
   <si>
+    <t>ClinicalDocument.documentationOf.serviceEvent.lab:statusCode</t>
+  </si>
+  <si>
+    <t>EnteteDocument.patient</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.recordTarget</t>
+  </si>
+  <si>
+    <t>EnteteDocument.auteur</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.author</t>
+  </si>
+  <si>
+    <t>EnteteDocument.operateurSaisie</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.dataEnterer</t>
+  </si>
+  <si>
+    <t>EnteteDocument.informateur</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.informant</t>
+  </si>
+  <si>
+    <t>EnteteDocument.structureConservation</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.custodian</t>
+  </si>
+  <si>
+    <t>EnteteDocument.destinataire</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.informationRecipient</t>
+  </si>
+  <si>
+    <t>EnteteDocument.responsable</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>EnteteDocument.validateur</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.authenticator</t>
+  </si>
+  <si>
+    <t>EnteteDocument.participant</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.participant</t>
+  </si>
+  <si>
+    <t>EnteteDocument.prescription</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.inFulfillmentOf</t>
+  </si>
+  <si>
+    <t>EnteteDocument.evenement</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.documentationOf</t>
+  </si>
+  <si>
+    <t>EnteteDocument.documentReference</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.relatedDocument</t>
+  </si>
+  <si>
+    <t>EnteteDocument.consentementAssocie</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.authorization</t>
+  </si>
+  <si>
+    <t>EnteteDocument.associationPriseEncharge</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.componentOf</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-bundle-document</t>
+  </si>
+  <si>
+    <t>Bundle.identifier</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+  </si>
+  <si>
+    <t>Composition.meta.profile</t>
+  </si>
+  <si>
+    <t>Composition.code</t>
+  </si>
+  <si>
+    <t>Composition.title</t>
+  </si>
+  <si>
+    <t>Composition.date</t>
+  </si>
+  <si>
+    <t>Composition.confidentiality</t>
+  </si>
+  <si>
+    <t>Composition.language</t>
+  </si>
+  <si>
+    <t>Composition.identifier</t>
+  </si>
+  <si>
+    <t>Composition.extension:R5-Composition-version</t>
+  </si>
+  <si>
     <t>ClinicalDocument.documentationOf.serviceEvent.statusCode</t>
-  </si>
-  <si>
-    <t>EnteteDocument.patient</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.recordTarget</t>
-  </si>
-  <si>
-    <t>EnteteDocument.auteur</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.author</t>
-  </si>
-  <si>
-    <t>EnteteDocument.operateurSaisie</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.dataEnterer</t>
-  </si>
-  <si>
-    <t>EnteteDocument.informateur</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.informant</t>
-  </si>
-  <si>
-    <t>EnteteDocument.structureConservation</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.custodian</t>
-  </si>
-  <si>
-    <t>EnteteDocument.destinataire</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.informationRecipient</t>
-  </si>
-  <si>
-    <t>EnteteDocument.responsable</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>EnteteDocument.validateur</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.authenticator</t>
-  </si>
-  <si>
-    <t>EnteteDocument.participant</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.participant</t>
-  </si>
-  <si>
-    <t>EnteteDocument.associationPrescription</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.inFulfillmentOf</t>
-  </si>
-  <si>
-    <t>EnteteDocument.evenement</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.documentationOf</t>
-  </si>
-  <si>
-    <t>EnteteDocument.documentReference</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.relatedDocument</t>
-  </si>
-  <si>
-    <t>EnteteDocument.consentementAssocie</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.authorization</t>
-  </si>
-  <si>
-    <t>EnteteDocument.associationPriseEncharge</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.componentOf</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-bundle-document</t>
-  </si>
-  <si>
-    <t>Bundle.identifier</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
-  </si>
-  <si>
-    <t>Composition.meta.profile</t>
-  </si>
-  <si>
-    <t>Composition.code</t>
-  </si>
-  <si>
-    <t>Composition.title</t>
-  </si>
-  <si>
-    <t>Composition.date</t>
-  </si>
-  <si>
-    <t>Composition.confidentiality</t>
-  </si>
-  <si>
-    <t>Composition.language</t>
-  </si>
-  <si>
-    <t>Composition.identifier</t>
-  </si>
-  <si>
-    <t>Composition.extension:R5-Composition-version</t>
   </si>
   <si>
     <t>Composition.status</t>
@@ -1150,14 +1153,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -1170,7 +1173,7 @@
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -1183,7 +1186,7 @@
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -1196,7 +1199,7 @@
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -1209,7 +1212,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -1222,7 +1225,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1235,7 +1238,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1248,7 +1251,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -1261,7 +1264,7 @@
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -1274,7 +1277,7 @@
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" s="2"/>
     </row>
@@ -1287,7 +1290,7 @@
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E21" s="2"/>
     </row>
@@ -1300,7 +1303,7 @@
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" s="2"/>
     </row>
@@ -1313,7 +1316,7 @@
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2"/>
     </row>
@@ -1326,7 +1329,7 @@
         <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
     </row>
@@ -1339,7 +1342,7 @@
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" s="2"/>
     </row>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -248,7 +248,7 @@
     <t>ClinicalDocument.documentationOf</t>
   </si>
   <si>
-    <t>EnteteDocument.documentReference</t>
+    <t>EnteteDocument.documentDeReference</t>
   </si>
   <si>
     <t>ClinicalDocument.relatedDocument</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
     <t>ClinicalDocument.authorization</t>
   </si>
   <si>
-    <t>EnteteDocument.associationPriseEncharge</t>
+    <t>EnteteDocument.priseEncharge</t>
   </si>
   <si>
     <t>ClinicalDocument.componentOf</t>
@@ -278,7 +278,7 @@
     <t>Composition.meta.profile</t>
   </si>
   <si>
-    <t>Composition.code</t>
+    <t>Composition.type</t>
   </si>
   <si>
     <t>Composition.title</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="107">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -297,9 +297,6 @@
   </si>
   <si>
     <t>Composition.extension:R5-Composition-version</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.documentationOf.serviceEvent.statusCode</t>
   </si>
   <si>
     <t>Composition.status</t>
@@ -1153,14 +1150,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -1173,7 +1170,7 @@
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -1186,7 +1183,7 @@
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -1199,7 +1196,7 @@
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -1212,7 +1209,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -1225,7 +1222,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1238,7 +1235,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1251,7 +1248,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -1264,7 +1261,7 @@
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -1277,7 +1274,7 @@
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="2"/>
     </row>
@@ -1290,7 +1287,7 @@
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" s="2"/>
     </row>
@@ -1303,7 +1300,7 @@
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E22" s="2"/>
     </row>
@@ -1316,7 +1313,7 @@
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2"/>
     </row>
@@ -1329,7 +1326,7 @@
         <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2"/>
     </row>
@@ -1342,7 +1339,7 @@
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2"/>
     </row>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -38,15 +38,12 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mapping du modèle logique métier de l'en-tête/CDA/FHIR</t>
+    <t>Mapping Métier/CDA/FHIR  : Entête d'un document</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Mapping du modèle logique métier de l'en-tête /CDA / FHIR</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -62,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,10 +83,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce ConceptMap présente trois groupes de mapping :
- - Groupe Mapping 1 : entre le modèle logique métier de l'en-tête et l'élément CDA clinicalDocument
- - Groupe Mapping 2 : entre l'élément CDA clinicalDocument et le profil FHIR FrBundleDocument
- - Groupe Mapping 3 : entre l'élément CDA clinicalDocument et le profil FHIR FrCompositionDocument</t>
+    <t xml:space="preserve">Ce ConceptMap présente trois groupes de mapping :
+ - Mapping 1 : entre le modèle métier \"EnteteDocument\" et l'élément CDA \"clinicalDocument\"
+ - Mapping 2 : entre l'élément CDA \"clinicalDocument\" et le profil FHIR \"FrBundleDocument\"
+ - Mapping 3 : entre l'élément CDA \"clinicalDocument\" et le profil FHIR \"FrCompositionDocument\" </t>
   </si>
   <si>
     <t>Purpose</t>
@@ -308,25 +305,25 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t>Composition.DataEntererExtension</t>
-  </si>
-  <si>
-    <t>Composition.extension:InformantExtension</t>
+    <t>Composition.extension:data-enterer</t>
+  </si>
+  <si>
+    <t>Composition.extension:informant</t>
   </si>
   <si>
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t>Composition.extension:InformationRecipientExtension</t>
+    <t>Composition.extension:informationRecipient</t>
   </si>
   <si>
     <t>Composition.attester</t>
   </si>
   <si>
-    <t>Composition.extension:ParticipantExtension</t>
-  </si>
-  <si>
-    <t>Composition.extension:OrderExtension</t>
+    <t>Composition.extension:participant</t>
+  </si>
+  <si>
+    <t>Composition.extension:order</t>
   </si>
   <si>
     <t>Composition.event</t>
@@ -335,7 +332,7 @@
     <t>Composition.relatesTo</t>
   </si>
   <si>
-    <t>Composition.extension:ConsentExtension</t>
+    <t>Composition.extension:consent</t>
   </si>
   <si>
     <t>Composition.encounter</t>
@@ -516,74 +513,74 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -599,347 +596,347 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
     </row>
@@ -955,48 +952,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1012,334 +1009,334 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E25" s="2"/>
     </row>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
